--- a/ecosysem/db/Excels/Cpi.xlsx
+++ b/ecosysem/db/Excels/Cpi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emartinez\Documents\GitHub\EcoSysEM\ecosysem\db\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE5BB0DD-C10A-4D33-8F10-F714743BC07D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5402C0-58A7-47C5-9B8A-140FF07B1B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A62AFDAB-FBC8-40CE-9878-3FD750A8957F}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{A62AFDAB-FBC8-40CE-9878-3FD750A8957F}"/>
   </bookViews>
   <sheets>
     <sheet name="Cpi" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="66">
   <si>
     <t>IUPAC</t>
   </si>
@@ -258,6 +258,9 @@
   </si>
   <si>
     <t>CO</t>
+  </si>
+  <si>
+    <t>G</t>
   </si>
 </sst>
 </file>
@@ -301,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -311,6 +314,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -665,17 +672,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC731D4-E3C1-4B64-BF1D-C3C9432561A9}">
-  <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -692,462 +699,547 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="4">
+      <c r="C2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="6">
+        <v>28.84</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="4">
         <v>20.526690391459073</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="4">
-        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="4">
+        <v>29.4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="4">
+        <v>21</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="C6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="4">
+        <v>33.6</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="4">
         <v>75.349999999999994</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="E7" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="C8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="4">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="E8" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="C9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="4">
         <v>293</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="E9" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="C10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="4">
         <v>-84</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="E10" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="C11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="4">
         <v>-293</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="E11" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="4">
+      <c r="C12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="4">
         <v>76.5</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="C13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="4">
         <v>-57.74</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="4">
+      <c r="C14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="4">
         <v>-204.18</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="C15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="4">
         <v>98.1</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="4">
+      <c r="C16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="4">
         <v>-87.9</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="E16" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="4">
+      <c r="C17" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="4">
         <v>137</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="4">
+      <c r="C18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="4">
         <v>-6.3</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="E18" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="4">
+      <c r="C19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="4">
         <v>37.130000000000003</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="E19" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="4">
+        <v>37.130000000000003</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="4">
+      <c r="C21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" s="4">
+        <v>29.14</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="4">
         <v>29.15</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="4">
+      <c r="C23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="4">
         <v>-200.83199999999999</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B24" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="4">
+      <c r="C24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="4">
         <v>-631.78399999999999</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B25" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="4">
+      <c r="C25" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="4">
         <v>99.2</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="E25" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B26" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" s="4">
+      <c r="C26" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="4">
         <v>81.464999999999989</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="4">
-        <v>79.900000000000006</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="4">
-        <v>27.4</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" s="4">
-        <v>109.9</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" s="4">
-        <v>-86.6</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" s="4">
-        <v>27.297254404062848</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="4">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="4">
+        <v>27.4</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="4">
+        <v>109.9</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" s="4">
+        <v>-86.6</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" s="4">
+        <v>27.297254404062848</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B32" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="4">
+      <c r="C32" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="4">
         <v>-97.5</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="E32" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B33" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" s="4">
+      <c r="C33" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="4">
         <v>29.123999999999999</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>48</v>
       </c>
     </row>

--- a/ecosysem/db/Excels/Cpi.xlsx
+++ b/ecosysem/db/Excels/Cpi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emartinez\Documents\GitHub\EcoSysEM\ecosysem\db\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5402C0-58A7-47C5-9B8A-140FF07B1B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C661C371-C384-440B-A4BA-44C43AFAAB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{A62AFDAB-FBC8-40CE-9878-3FD750A8957F}"/>
+    <workbookView xWindow="14175" yWindow="-21600" windowWidth="19410" windowHeight="20985" xr2:uid="{A62AFDAB-FBC8-40CE-9878-3FD750A8957F}"/>
   </bookViews>
   <sheets>
     <sheet name="Cpi" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="66">
   <si>
     <t>IUPAC</t>
   </si>
@@ -304,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -314,10 +314,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -672,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC731D4-E3C1-4B64-BF1D-C3C9432561A9}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -700,19 +696,19 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="3">
         <v>28.84</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1241,6 +1237,40 @@
       </c>
       <c r="E33" s="3" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="3">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" s="3">
+        <v>27.4</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/ecosysem/db/Excels/Cpi.xlsx
+++ b/ecosysem/db/Excels/Cpi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emartinez\Documents\GitHub\EcoSysEM\ecosysem\db\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C661C371-C384-440B-A4BA-44C43AFAAB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0AC4CC-54EA-4953-9CCA-6DB784749D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14175" yWindow="-21600" windowWidth="19410" windowHeight="20985" xr2:uid="{A62AFDAB-FBC8-40CE-9878-3FD750A8957F}"/>
+    <workbookView xWindow="-5040" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{A62AFDAB-FBC8-40CE-9878-3FD750A8957F}"/>
   </bookViews>
   <sheets>
     <sheet name="Cpi" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="66">
   <si>
     <t>IUPAC</t>
   </si>
@@ -668,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC731D4-E3C1-4B64-BF1D-C3C9432561A9}">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -1256,23 +1256,6 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" s="3">
-        <v>27.4</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
